--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.8672448901726</v>
+        <v>12.16592729465305</v>
       </c>
       <c r="D2" t="n">
-        <v>75.13218402195618</v>
+        <v>12.20897990356788</v>
       </c>
       <c r="E2" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F2" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.465061640172305</v>
+        <v>1.375572516528</v>
       </c>
       <c r="D3" t="n">
-        <v>8.489274278628166</v>
+        <v>1.379507070277077</v>
       </c>
       <c r="E3" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F3" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.73836579745726</v>
+        <v>1.744984442086805</v>
       </c>
       <c r="D4" t="n">
-        <v>17.00576419440348</v>
+        <v>2.763436681590565</v>
       </c>
       <c r="E4" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F4" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.45760347073572</v>
+        <v>6.249360563994554</v>
       </c>
       <c r="D5" t="n">
-        <v>38.58038370531116</v>
+        <v>6.269312352113064</v>
       </c>
       <c r="E5" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F5" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.00035060780051</v>
+        <v>3.412556973767583</v>
       </c>
       <c r="D6" t="n">
-        <v>21.28482351488626</v>
+        <v>3.458783821169017</v>
       </c>
       <c r="E6" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F6" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.93008622036315</v>
+        <v>4.538639010809012</v>
       </c>
       <c r="D7" t="n">
-        <v>33.609139637959</v>
+        <v>5.461485191168337</v>
       </c>
       <c r="E7" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F7" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.94370143659614</v>
+        <v>6.003351483446873</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71182767786242</v>
+        <v>5.965671997652644</v>
       </c>
       <c r="E8" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F8" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.75996108294244</v>
+        <v>3.210993675978146</v>
       </c>
       <c r="D9" t="n">
-        <v>19.66099954492319</v>
+        <v>3.194912426050018</v>
       </c>
       <c r="E9" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F9" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.31412511212401</v>
+        <v>2.326045330720151</v>
       </c>
       <c r="D10" t="n">
-        <v>14.33097404811302</v>
+        <v>2.328783282818365</v>
       </c>
       <c r="E10" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F10" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.67853426503927</v>
+        <v>6.772761818068881</v>
       </c>
       <c r="D11" t="n">
-        <v>41.81536926291387</v>
+        <v>6.794997505223504</v>
       </c>
       <c r="E11" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F11" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.43579156976815</v>
+        <v>6.245816130087325</v>
       </c>
       <c r="D12" t="n">
-        <v>37.97666603551237</v>
+        <v>6.17120823077076</v>
       </c>
       <c r="E12" t="n">
-        <v>18.11755466731586</v>
+        <v>2.944102633438828</v>
       </c>
       <c r="F12" t="n">
-        <v>17.61301039119245</v>
+        <v>2.862114188568774</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
